--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-specimen-common.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-specimen-common.xlsx
@@ -434,7 +434,7 @@
     <t>Specimen.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -472,7 +472,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -717,7 +717,7 @@
     <t>Specimen.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Substance|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Substance|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -761,7 +761,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -780,7 +780,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -842,7 +842,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -899,7 +899,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1036,7 +1036,7 @@
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance)
+    <t xml:space="preserve">Reference(Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1155,7 +1155,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>採取容器の添加物（ CodeableConcept または Reference(Substance) のどちらか）</t>
@@ -1546,7 +1546,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="42.890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.53515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
